--- a/Project_Duel/Assets/StreamingAssets/Cards.xlsx
+++ b/Project_Duel/Assets/StreamingAssets/Cards.xlsx
@@ -516,7 +516,7 @@
     <t>在你的主要阶段中限一次，你可以将任意张手牌放置在此角色牌上。在你的弃牌阶段结束时，若此角色牌上的牌的点数之和不小于36，你可以将此角色上的所有牌置入弃牌堆，并造成6点雷电伤害。若你以此法置入弃牌堆的牌颜色相同，你改为造成8点雷电伤害。</t>
   </si>
   <si>
-    <t>卢植</t>
+    <t>皇甫嵩</t>
   </si>
   <si>
     <t>汉</t>
@@ -540,7 +540,7 @@
     <t>当一名玩家获得效果时，你可以选择一项：1. 恢复1点生命；2. 造成1点通用伤害。</t>
   </si>
   <si>
-    <t>皇甫嵩</t>
+    <t>卢植</t>
   </si>
   <si>
     <t>经天纬地</t>
@@ -2680,8 +2680,8 @@
       <c r="D23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="3">
-        <v>2</v>
+      <c r="E23" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>31</v>
@@ -2735,8 +2735,8 @@
       <c r="D25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>115</v>
+      <c r="E25" s="3">
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>31</v>
